--- a/schoolDocs/StudentImportData/Class2_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class2_ImportReady.xlsx
@@ -685,27 +685,27 @@
   <dimension ref="A1:U17"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="25.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="24.565" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="29.279" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="35.277" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="88.407" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.283" customWidth="true" style="0"/>
+    <col min="2" max="2" width="26.993" customWidth="true" style="0"/>
+    <col min="3" max="3" width="18.71" customWidth="true" style="0"/>
+    <col min="4" max="4" width="10.426" customWidth="true" style="0"/>
+    <col min="5" max="5" width="9.283" customWidth="true" style="0"/>
+    <col min="6" max="6" width="11.569" customWidth="true" style="0"/>
+    <col min="7" max="7" width="25.708" customWidth="true" style="0"/>
+    <col min="8" max="8" width="17.567" customWidth="true" style="0"/>
+    <col min="9" max="9" width="15.139" customWidth="true" style="0"/>
+    <col min="10" max="10" width="24.565" customWidth="true" style="0"/>
+    <col min="11" max="11" width="29.279" customWidth="true" style="0"/>
+    <col min="12" max="12" width="35.277" customWidth="true" style="0"/>
+    <col min="13" max="13" width="12.854" customWidth="true" style="0"/>
+    <col min="14" max="14" width="26.993" customWidth="true" style="0"/>
+    <col min="15" max="15" width="16.282" customWidth="true" style="0"/>
+    <col min="16" max="16" width="23.423" customWidth="true" style="0"/>
+    <col min="17" max="17" width="16.282" customWidth="true" style="0"/>
+    <col min="18" max="18" width="23.423" customWidth="true" style="0"/>
+    <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
+    <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
+    <col min="21" max="21" width="88.407" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -795,6 +795,11 @@
       <c r="H2" t="s">
         <v>25</v>
       </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2">
+        <v>16200</v>
+      </c>
       <c r="L2" t="s">
         <v>26</v>
       </c>
@@ -833,6 +838,11 @@
       <c r="H3" t="s">
         <v>32</v>
       </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3">
+        <v>0</v>
+      </c>
       <c r="L3" t="s">
         <v>33</v>
       </c>
@@ -874,6 +884,11 @@
       <c r="H4" t="s">
         <v>32</v>
       </c>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4">
+        <v>0</v>
+      </c>
       <c r="L4" t="s">
         <v>39</v>
       </c>
@@ -915,6 +930,11 @@
       <c r="H5" t="s">
         <v>25</v>
       </c>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5">
+        <v>16200</v>
+      </c>
       <c r="L5" t="s">
         <v>44</v>
       </c>
@@ -947,11 +967,12 @@
       <c r="H6" t="s">
         <v>46</v>
       </c>
+      <c r="I6"/>
       <c r="J6">
         <v>2000</v>
       </c>
       <c r="K6">
-        <v>2000</v>
+        <v>2000.0</v>
       </c>
       <c r="L6" t="s">
         <v>47</v>
@@ -988,8 +1009,10 @@
       <c r="H7" t="s">
         <v>25</v>
       </c>
+      <c r="I7"/>
+      <c r="J7"/>
       <c r="K7" s="5">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="L7" t="s">
         <v>52</v>
@@ -1026,6 +1049,11 @@
       <c r="H8" t="s">
         <v>32</v>
       </c>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8">
+        <v>0</v>
+      </c>
       <c r="L8" t="s">
         <v>56</v>
       </c>
@@ -1058,6 +1086,8 @@
       <c r="H9" t="s">
         <v>60</v>
       </c>
+      <c r="I9"/>
+      <c r="J9"/>
       <c r="K9">
         <v>16200</v>
       </c>
@@ -1096,6 +1126,11 @@
       <c r="H10" t="s">
         <v>32</v>
       </c>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10">
+        <v>0</v>
+      </c>
       <c r="L10" t="s">
         <v>64</v>
       </c>
@@ -1128,6 +1163,8 @@
       <c r="H11" t="s">
         <v>60</v>
       </c>
+      <c r="I11"/>
+      <c r="J11"/>
       <c r="K11">
         <v>16200</v>
       </c>
@@ -1163,8 +1200,10 @@
       <c r="H12" t="s">
         <v>60</v>
       </c>
+      <c r="I12"/>
+      <c r="J12"/>
       <c r="K12">
-        <v>12200</v>
+        <v>16200</v>
       </c>
       <c r="L12" t="s">
         <v>70</v>
@@ -1201,6 +1240,8 @@
       <c r="H13" t="s">
         <v>25</v>
       </c>
+      <c r="I13"/>
+      <c r="J13"/>
       <c r="K13">
         <v>12200</v>
       </c>
@@ -1236,6 +1277,8 @@
       <c r="H14" t="s">
         <v>25</v>
       </c>
+      <c r="I14"/>
+      <c r="J14"/>
       <c r="K14">
         <v>12200</v>
       </c>
@@ -1280,6 +1323,7 @@
       <c r="I15">
         <v>25</v>
       </c>
+      <c r="J15"/>
       <c r="K15">
         <v>9150</v>
       </c>
@@ -1327,6 +1371,10 @@
       <c r="I16">
         <v>25</v>
       </c>
+      <c r="J16"/>
+      <c r="K16">
+        <v>9150</v>
+      </c>
       <c r="L16" t="s">
         <v>85</v>
       </c>
@@ -1364,6 +1412,11 @@
       </c>
       <c r="H17" t="s">
         <v>32</v>
+      </c>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17">
+        <v>0</v>
       </c>
       <c r="L17" t="s">
         <v>89</v>

--- a/schoolDocs/StudentImportData/Class2_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class2_ImportReady.xlsx
@@ -14,8 +14,34 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="U1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Calibri"/>
+            <b val="false"/>
+            <i val="false"/>
+            <strike val="false"/>
+            <color rgb="FF000000"/>
+            <sz val="11"/>
+            <u val="none"/>
+          </rPr>
+          <t xml:space="preserve">Only for RTE students. Alphanumeric, e.g. 26MS011157 (Year+StateCode+Sequence). Leave blank for non-RTE.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="89">
   <si>
     <t>Sr No</t>
   </si>
@@ -77,7 +103,7 @@
     <t>DGA Admission No</t>
   </si>
   <si>
-    <t>Notes for Verification (ignored on import)</t>
+    <t>RTE Application No</t>
   </si>
   <si>
     <t>Ayaan Masjid Tamboli</t>
@@ -128,7 +154,7 @@
     <t>Vegetable shop</t>
   </si>
   <si>
-    <t>RTE — fees paid by government</t>
+    <t>25MS000012</t>
   </si>
   <si>
     <t>Shrikar Sahin Dolare</t>
@@ -146,6 +172,9 @@
     <t>Works at Sayadri</t>
   </si>
   <si>
+    <t>25MS000013</t>
+  </si>
+  <si>
     <t>Vaibhav Lavhaji Kokare</t>
   </si>
   <si>
@@ -167,9 +196,6 @@
     <t>19km</t>
   </si>
   <si>
-    <t>DGA shows ₹2000 custom fee — collected in full. Please verify category.</t>
-  </si>
-  <si>
     <t>Ankur Satyendar Gautam</t>
   </si>
   <si>
@@ -179,9 +205,6 @@
     <t>Kedgaon</t>
   </si>
   <si>
-    <t>Partial — ₹5400 of ₹16200 collected</t>
-  </si>
-  <si>
     <t>Ayaaj Riyaz Pathan</t>
   </si>
   <si>
@@ -194,6 +217,9 @@
     <t>11km</t>
   </si>
   <si>
+    <t>25MS000014</t>
+  </si>
+  <si>
     <t>Arman Abdul Shaikh</t>
   </si>
   <si>
@@ -203,9 +229,6 @@
     <t>11/02/2022</t>
   </si>
   <si>
-    <t>CoC student — full ₹16200 collected</t>
-  </si>
-  <si>
     <t>Sangram Gopal Dagade</t>
   </si>
   <si>
@@ -218,6 +241,9 @@
     <t>500meter</t>
   </si>
   <si>
+    <t>25MS000015</t>
+  </si>
+  <si>
     <t>Karan Manoj Gaikwad</t>
   </si>
   <si>
@@ -230,9 +256,6 @@
     <t>29/01/2022</t>
   </si>
   <si>
-    <t>DGA shows ₹12200 for this CoC boy — system will use ₹16200. Please verify.</t>
-  </si>
-  <si>
     <t>Rajvee Ashok Tadge</t>
   </si>
   <si>
@@ -266,9 +289,6 @@
     <t>Sight Contractor</t>
   </si>
   <si>
-    <t>Discount 25% on girls fee ₹12200 = ₹9150 payable — full paid</t>
-  </si>
-  <si>
     <t>Aarohi Malhari Hake</t>
   </si>
   <si>
@@ -278,9 +298,6 @@
     <t>Farmer at own farm</t>
   </si>
   <si>
-    <t>Discount 25% on girls fee ₹12200 = ₹9150 payable — collected ₹0</t>
-  </si>
-  <si>
     <t>Sonali Somnath Thorat</t>
   </si>
   <si>
@@ -288,6 +305,9 @@
   </si>
   <si>
     <t>Varvand</t>
+  </si>
+  <si>
+    <t>25MS000016</t>
   </si>
 </sst>
 </file>
@@ -339,12 +359,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7B3F00"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
@@ -352,6 +366,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD5EAD0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E4057"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -373,16 +393,16 @@
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -705,7 +725,7 @@
     <col min="18" max="18" width="23.423" customWidth="true" style="0"/>
     <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
     <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
-    <col min="21" max="21" width="88.407" customWidth="true" style="0"/>
+    <col min="21" max="21" width="20" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -739,10 +759,10 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -769,7 +789,7 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -815,6 +835,7 @@
       <c r="R2" t="s">
         <v>30</v>
       </c>
+      <c r="U2"/>
     </row>
     <row r="3" spans="1:21">
       <c r="A3">
@@ -905,7 +926,7 @@
         <v>30</v>
       </c>
       <c r="U4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -913,7 +934,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -936,7 +957,7 @@
         <v>16200</v>
       </c>
       <c r="L5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M5" t="s">
         <v>27</v>
@@ -944,13 +965,14 @@
       <c r="N5" t="s">
         <v>28</v>
       </c>
+      <c r="U5"/>
     </row>
     <row r="6" spans="1:21">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -965,7 +987,7 @@
         <v>9172104521</v>
       </c>
       <c r="H6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I6"/>
       <c r="J6">
@@ -975,17 +997,15 @@
         <v>2000.0</v>
       </c>
       <c r="L6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N6" t="s">
-        <v>49</v>
-      </c>
-      <c r="U6" s="5" t="s">
         <v>50</v>
       </c>
+      <c r="U6" s="4"/>
     </row>
     <row r="7" spans="1:21">
       <c r="A7">
@@ -1011,7 +1031,7 @@
       </c>
       <c r="I7"/>
       <c r="J7"/>
-      <c r="K7" s="5">
+      <c r="K7" s="4">
         <v>0</v>
       </c>
       <c r="L7" t="s">
@@ -1023,16 +1043,14 @@
       <c r="N7" t="s">
         <v>35</v>
       </c>
-      <c r="U7" s="5" t="s">
-        <v>54</v>
-      </c>
+      <c r="U7" s="4"/>
     </row>
     <row r="8" spans="1:21">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
@@ -1055,16 +1073,16 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" t="s">
         <v>56</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>57</v>
       </c>
-      <c r="N8" t="s">
+      <c r="U8" t="s">
         <v>58</v>
-      </c>
-      <c r="U8" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -1095,21 +1113,19 @@
         <v>61</v>
       </c>
       <c r="M9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N9" t="s">
-        <v>49</v>
-      </c>
-      <c r="U9" t="s">
-        <v>62</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="U9"/>
     </row>
     <row r="10" spans="1:21">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
@@ -1132,16 +1148,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
+        <v>63</v>
+      </c>
+      <c r="M10" t="s">
         <v>64</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>65</v>
       </c>
-      <c r="N10" t="s">
+      <c r="U10" t="s">
         <v>66</v>
-      </c>
-      <c r="U10" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1172,14 +1188,12 @@
         <v>68</v>
       </c>
       <c r="M11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N11" t="s">
-        <v>49</v>
-      </c>
-      <c r="U11" t="s">
-        <v>62</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="U11"/>
     </row>
     <row r="12" spans="1:21">
       <c r="A12">
@@ -1209,24 +1223,22 @@
         <v>70</v>
       </c>
       <c r="M12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N12" t="s">
-        <v>49</v>
-      </c>
-      <c r="U12" s="5" t="s">
-        <v>71</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="U12" s="4"/>
     </row>
     <row r="13" spans="1:21">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" t="s">
         <v>72</v>
-      </c>
-      <c r="D13" t="s">
-        <v>73</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
@@ -1246,7 +1258,7 @@
         <v>12200</v>
       </c>
       <c r="L13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M13" t="s">
         <v>34</v>
@@ -1254,16 +1266,17 @@
       <c r="N13" t="s">
         <v>35</v>
       </c>
+      <c r="U13"/>
     </row>
     <row r="14" spans="1:21">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
@@ -1283,7 +1296,7 @@
         <v>12200</v>
       </c>
       <c r="L14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M14" t="s">
         <v>27</v>
@@ -1292,21 +1305,22 @@
         <v>28</v>
       </c>
       <c r="P14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R14" t="s">
         <v>30</v>
       </c>
+      <c r="U14"/>
     </row>
     <row r="15" spans="1:21">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
@@ -1318,7 +1332,7 @@
         <v>9834918810</v>
       </c>
       <c r="H15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I15">
         <v>25</v>
@@ -1328,33 +1342,31 @@
         <v>9150</v>
       </c>
       <c r="L15" t="s">
+        <v>78</v>
+      </c>
+      <c r="M15" t="s">
         <v>79</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>80</v>
       </c>
-      <c r="N15" t="s">
+      <c r="P15" t="s">
         <v>81</v>
-      </c>
-      <c r="P15" t="s">
-        <v>82</v>
       </c>
       <c r="R15" t="s">
         <v>30</v>
       </c>
-      <c r="U15" t="s">
-        <v>83</v>
-      </c>
+      <c r="U15"/>
     </row>
     <row r="16" spans="1:21">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
@@ -1366,7 +1378,7 @@
         <v>9021176633</v>
       </c>
       <c r="H16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I16">
         <v>25</v>
@@ -1376,7 +1388,7 @@
         <v>9150</v>
       </c>
       <c r="L16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M16" t="s">
         <v>27</v>
@@ -1385,24 +1397,22 @@
         <v>28</v>
       </c>
       <c r="P16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="R16" t="s">
         <v>30</v>
       </c>
-      <c r="U16" t="s">
-        <v>87</v>
-      </c>
+      <c r="U16"/>
     </row>
     <row r="17" spans="1:21">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
         <v>23</v>
@@ -1419,16 +1429,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="N17" t="s">
         <v>35</v>
       </c>
       <c r="U17" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1443,6 +1453,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId_comments_vml1"/>
   <tableParts count="0"/>
 </worksheet>
 </file>
--- a/schoolDocs/StudentImportData/Class2_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class2_ImportReady.xlsx
@@ -835,6 +835,9 @@
       <c r="R2" t="s">
         <v>30</v>
       </c>
+      <c r="S2">
+        <v>27000010020</v>
+      </c>
       <c r="U2"/>
     </row>
     <row r="3" spans="1:21">
@@ -879,6 +882,9 @@
       <c r="R3" t="s">
         <v>30</v>
       </c>
+      <c r="S3">
+        <v>27000010021</v>
+      </c>
       <c r="U3" t="s">
         <v>37</v>
       </c>
@@ -925,6 +931,9 @@
       <c r="R4" t="s">
         <v>30</v>
       </c>
+      <c r="S4">
+        <v>27000010022</v>
+      </c>
       <c r="U4" t="s">
         <v>43</v>
       </c>
@@ -965,6 +974,9 @@
       <c r="N5" t="s">
         <v>28</v>
       </c>
+      <c r="S5">
+        <v>27000010023</v>
+      </c>
       <c r="U5"/>
     </row>
     <row r="6" spans="1:21">
@@ -1004,6 +1016,9 @@
       </c>
       <c r="N6" t="s">
         <v>50</v>
+      </c>
+      <c r="S6">
+        <v>27000010024</v>
       </c>
       <c r="U6" s="4"/>
     </row>
@@ -1043,6 +1058,9 @@
       <c r="N7" t="s">
         <v>35</v>
       </c>
+      <c r="S7">
+        <v>27000010025</v>
+      </c>
       <c r="U7" s="4"/>
     </row>
     <row r="8" spans="1:21">
@@ -1081,6 +1099,9 @@
       <c r="N8" t="s">
         <v>57</v>
       </c>
+      <c r="S8">
+        <v>27000010026</v>
+      </c>
       <c r="U8" t="s">
         <v>58</v>
       </c>
@@ -1118,6 +1139,9 @@
       <c r="N9" t="s">
         <v>50</v>
       </c>
+      <c r="S9">
+        <v>27000010027</v>
+      </c>
       <c r="U9"/>
     </row>
     <row r="10" spans="1:21">
@@ -1156,6 +1180,9 @@
       <c r="N10" t="s">
         <v>65</v>
       </c>
+      <c r="S10">
+        <v>27000010028</v>
+      </c>
       <c r="U10" t="s">
         <v>66</v>
       </c>
@@ -1193,6 +1220,9 @@
       <c r="N11" t="s">
         <v>50</v>
       </c>
+      <c r="S11">
+        <v>27000010029</v>
+      </c>
       <c r="U11"/>
     </row>
     <row r="12" spans="1:21">
@@ -1228,6 +1258,9 @@
       <c r="N12" t="s">
         <v>50</v>
       </c>
+      <c r="S12">
+        <v>27000010030</v>
+      </c>
       <c r="U12" s="4"/>
     </row>
     <row r="13" spans="1:21">
@@ -1266,6 +1299,9 @@
       <c r="N13" t="s">
         <v>35</v>
       </c>
+      <c r="S13">
+        <v>27000010031</v>
+      </c>
       <c r="U13"/>
     </row>
     <row r="14" spans="1:21">
@@ -1310,6 +1346,9 @@
       <c r="R14" t="s">
         <v>30</v>
       </c>
+      <c r="S14">
+        <v>27000010032</v>
+      </c>
       <c r="U14"/>
     </row>
     <row r="15" spans="1:21">
@@ -1356,6 +1395,9 @@
       <c r="R15" t="s">
         <v>30</v>
       </c>
+      <c r="S15">
+        <v>27000010033</v>
+      </c>
       <c r="U15"/>
     </row>
     <row r="16" spans="1:21">
@@ -1401,6 +1443,9 @@
       </c>
       <c r="R16" t="s">
         <v>30</v>
+      </c>
+      <c r="S16">
+        <v>27000010034</v>
       </c>
       <c r="U16"/>
     </row>
@@ -1436,6 +1481,9 @@
       </c>
       <c r="N17" t="s">
         <v>35</v>
+      </c>
+      <c r="S17">
+        <v>27000010035</v>
       </c>
       <c r="U17" t="s">
         <v>88</v>
